--- a/nr-add-lipids/ig/StructureDefinition-mesures-cholesterol-diagnostic-report.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-cholesterol-diagnostic-report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="349">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T12:31:04+00:00</t>
+    <t>2025-03-04T08:19:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -329,17 +329,10 @@
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>DiagnosticReport.implicitRules</t>
   </si>
   <si>
@@ -359,9 +352,6 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>DiagnosticReport.language</t>
   </si>
   <si>
@@ -439,6 +429,9 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>DiagnosticReport.extension</t>
   </si>
   <si>
@@ -459,16 +452,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -550,10 +533,6 @@
     <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>Event.basedOn</t>
   </si>
   <si>
@@ -570,9 +549,6 @@
   </si>
   <si>
     <t>The status of the diagnostic report.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
@@ -645,9 +621,6 @@
   </si>
   <si>
     <t>A code or name that describes this diagnostic report.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -694,9 +667,6 @@
     <t>The subject of the report. Usually, but not always, this is a patient. However, diagnostic services also perform analyses on specimens collected from a variety of other sources.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>SHALL know the subject context.</t>
   </si>
   <si>
@@ -920,6 +890,9 @@
 </t>
   </si>
   <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>OBXs</t>
   </si>
   <si>
@@ -1024,6 +997,9 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>DiagnosticReport.media.extension</t>
   </si>
   <si>
@@ -1141,10 +1117,6 @@
   </si>
   <si>
     <t>Gives laboratory the ability to provide its own fully formatted report for clinical fidelity.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}</t>
   </si>
   <si>
     <t>text (type=ED)</t>
@@ -1495,7 +1467,7 @@
     <col min="26" max="26" width="53.546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
@@ -1952,11 +1924,11 @@
         <v>90</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>80</v>
       </c>
@@ -1964,7 +1936,7 @@
         <v>80</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AN4" t="s" s="2">
         <v>80</v>
@@ -1972,10 +1944,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1998,16 +1970,16 @@
         <v>91</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2057,7 +2029,7 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2066,11 +2038,11 @@
         <v>90</v>
       </c>
       <c r="AI5" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ5" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="AK5" t="s" s="2">
         <v>80</v>
       </c>
@@ -2078,7 +2050,7 @@
         <v>80</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>80</v>
@@ -2086,10 +2058,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2112,16 +2084,16 @@
         <v>80</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N6" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2147,31 +2119,31 @@
         <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -2180,11 +2152,11 @@
         <v>90</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
       </c>
@@ -2192,7 +2164,7 @@
         <v>80</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>80</v>
@@ -2200,14 +2172,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2226,16 +2198,16 @@
         <v>80</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2285,7 +2257,7 @@
         <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2294,11 +2266,11 @@
         <v>90</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>80</v>
       </c>
@@ -2306,7 +2278,7 @@
         <v>80</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>80</v>
@@ -2314,14 +2286,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2340,16 +2312,16 @@
         <v>80</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2399,7 +2371,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2420,7 +2392,7 @@
         <v>80</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>80</v>
@@ -2428,14 +2400,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2454,16 +2426,16 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2501,19 +2473,19 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2522,10 +2494,10 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
@@ -2534,7 +2506,7 @@
         <v>80</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>80</v>
@@ -2542,14 +2514,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2568,19 +2540,19 @@
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>80</v>
@@ -2617,19 +2589,19 @@
         <v>80</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2638,10 +2610,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
@@ -2650,7 +2622,7 @@
         <v>80</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>80</v>
@@ -2658,14 +2630,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2684,19 +2656,19 @@
         <v>91</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -2745,7 +2717,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2754,34 +2726,34 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="AK11" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2800,19 +2772,19 @@
         <v>80</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -2861,7 +2833,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2870,19 +2842,19 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AK12" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>80</v>
@@ -2890,10 +2862,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2916,19 +2888,17 @@
         <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>80</v>
@@ -2953,13 +2923,13 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -2977,7 +2947,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>90</v>
@@ -2986,34 +2956,34 @@
         <v>90</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="AK13" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3032,16 +3002,16 @@
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3067,13 +3037,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3091,7 +3061,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3100,34 +3070,34 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="AK14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3146,17 +3116,15 @@
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3166,7 +3134,7 @@
         <v>80</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>80</v>
@@ -3181,13 +3149,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3205,7 +3173,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>90</v>
@@ -3214,34 +3182,34 @@
         <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="AK15" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3260,19 +3228,17 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -3321,7 +3287,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3330,34 +3296,34 @@
         <v>90</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AK16" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3376,19 +3342,19 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3437,7 +3403,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3446,34 +3412,34 @@
         <v>90</v>
       </c>
       <c r="AI17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ17" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AK17" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3492,19 +3458,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3553,7 +3519,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3562,34 +3528,34 @@
         <v>90</v>
       </c>
       <c r="AI18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ18" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="AK18" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3608,19 +3574,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -3669,7 +3635,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3678,34 +3644,34 @@
         <v>90</v>
       </c>
       <c r="AI19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ19" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="AK19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3724,19 +3690,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -3785,7 +3751,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3794,34 +3760,34 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ20" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AK20" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3840,19 +3806,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -3901,7 +3867,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3910,30 +3876,30 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ21" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AK21" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>268</v>
-      </c>
       <c r="AM21" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3956,19 +3922,19 @@
         <v>80</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4017,7 +3983,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4026,19 +3992,19 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ22" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AK22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>80</v>
@@ -4046,18 +4012,18 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>79</v>
@@ -4072,19 +4038,19 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -4121,17 +4087,17 @@
         <v>80</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>144</v>
+        <v>276</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4140,19 +4106,19 @@
         <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ23" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AK23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>80</v>
@@ -4160,16 +4126,16 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4188,19 +4154,19 @@
         <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4249,7 +4215,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4258,19 +4224,19 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ24" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>80</v>
@@ -4278,16 +4244,16 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4306,19 +4272,19 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -4367,7 +4333,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4376,19 +4342,19 @@
         <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ25" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>80</v>
@@ -4396,16 +4362,16 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4424,19 +4390,19 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -4485,7 +4451,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4494,19 +4460,19 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ26" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AK26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>80</v>
@@ -4514,16 +4480,16 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4542,19 +4508,19 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -4603,7 +4569,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4612,19 +4578,19 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
@@ -4632,10 +4598,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4658,16 +4624,16 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4717,7 +4683,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4726,11 +4692,11 @@
         <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
       </c>
@@ -4738,7 +4704,7 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>80</v>
@@ -4746,14 +4712,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4772,17 +4738,17 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -4831,7 +4797,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4840,19 +4806,19 @@
         <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -4860,10 +4826,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4886,13 +4852,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4943,7 +4909,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4964,7 +4930,7 @@
         <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>111</v>
+        <v>309</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -4972,14 +4938,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4998,16 +4964,16 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5045,19 +5011,19 @@
         <v>80</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5066,10 +5032,10 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>80</v>
@@ -5078,7 +5044,7 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>104</v>
+        <v>309</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>80</v>
@@ -5086,14 +5052,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5112,19 +5078,19 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -5173,7 +5139,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5182,10 +5148,10 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>80</v>
@@ -5194,7 +5160,7 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5202,10 +5168,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5228,19 +5194,19 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5289,7 +5255,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5298,11 +5264,11 @@
         <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ33" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
       </c>
@@ -5310,7 +5276,7 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5318,10 +5284,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5344,17 +5310,15 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -5403,7 +5367,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>90</v>
@@ -5412,11 +5376,11 @@
         <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
       </c>
@@ -5424,7 +5388,7 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -5432,14 +5396,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5458,19 +5422,17 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -5519,7 +5481,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5528,19 +5490,19 @@
         <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -5548,10 +5510,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5574,17 +5536,15 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -5609,13 +5569,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -5633,7 +5593,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5642,19 +5602,19 @@
         <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -5662,10 +5622,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5688,19 +5648,19 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -5749,7 +5709,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5758,19 +5718,19 @@
         <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
